--- a/test-case-exports/PaymentLinks.xlsx
+++ b/test-case-exports/PaymentLinks.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -44,27 +44,144 @@
     <t>PaymentLinks</t>
   </si>
   <si>
+    <t>BusinessTestCases/PaymentLinks/functional/BillPaymentLinkBugs.spec.ts</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — OTP Max Attempts Handled Gracefully (BPL-01, EMI-5684)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>BPL-01: exceeding max OTP attempts on a bill payment link should not surface a 500 error</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>BPL-01 (regression guard): the pre-fix mock reproduces the raw 500 the bug ticket captured</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — Merchant-to-Merchant Link Resolves (BPL-02, EMI-5822)</t>
+  </si>
+  <si>
+    <t>BPL-02: a merchant-to-merchant bill link should resolve (not 500) so both a guest and a merchant payer can pay</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — All Payment Methods Offered (BPL-03, EMI-5830)</t>
+  </si>
+  <si>
+    <t>BPL-03: the payer should see every configured payment method, not only Mada</t>
+  </si>
+  <si>
+    <t>Gated: Payment method selection not shown for this link/environment</t>
+  </si>
+  <si>
+    <t>BPL-03 (regression guard): the pre-fix mock reproduces Mada-only</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — Payment Submission Succeeds (BPL-04, EMI-5633)</t>
+  </si>
+  <si>
+    <t>BPL-04: paying a bill payment link should succeed, not surface a 500 error</t>
+  </si>
+  <si>
+    <t>Gated: Continue button not shown for this link/environment</t>
+  </si>
+  <si>
+    <t>BPL-04 (regression guard): the pre-fix mock reproduces the 500 on submit</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — Unapproved Bill Rejected Gracefully (BPL-05, EMI-5526)</t>
+  </si>
+  <si>
+    <t>BPL-05: creating a payment link for an unapproved bill should show a clear message, not a 500 error</t>
+  </si>
+  <si>
+    <t>BPL-05 (regression guard): the pre-fix mock reproduces the raw 500 the bug ticket captured</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — Create-Link Action Hidden for Paid Bills (BPL-06, EMI-5527, EMI-5474)</t>
+  </si>
+  <si>
+    <t>BPL-06: the create-payment-link action should not be offered once a bill is already paid</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — Wallet/Bill Transfer Draft Succeeds (BPL-07, EMI-5513)</t>
+  </si>
+  <si>
+    <t>BPL-07: a wallet/bill payment transfer draft should succeed, not 404 with WALLET_TYPE_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>BPL-07 (regression guard): the pre-fix mock reproduces WALLET_TYPE_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — Bill Nav Resolves After Returning From Link Result (BPL-08, BPL-09, EMI-5630, EMI-5634)</t>
+  </si>
+  <si>
+    <t>BPL-08: the biller should still be authorized to view Bill Information after returning from a payment-link result</t>
+  </si>
+  <si>
+    <t>BPL-08 (regression guard): the pre-fix mock reproduces the 403 unauthorized response</t>
+  </si>
+  <si>
+    <t>BPL-09: the Bill page should render populated content, not an empty page, after returning from a payment-link result</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — Summary Displays the Amount (BPL-10, EMI-5619)</t>
+  </si>
+  <si>
+    <t>BPL-10: the bill payment summary should display the payable amount</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — Generation &amp; Resolution Reuse Bill Rules (BPL-11, EMI-5438, EMI-5443)</t>
+  </si>
+  <si>
+    <t>BPL-11: link resolution should return a sanitized summary including fees/VAT without exposing internal fields</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — Settled Link Reaches The Transactions List (BPL-12, EMI-5967)</t>
+  </si>
+  <si>
+    <t>BPL-12: a paid bill payment link is reflected in the payer transactions</t>
+  </si>
+  <si>
+    <t>BPL-12b: the reflected transaction carries a settled status</t>
+  </si>
+  <si>
+    <t>BPL-12 (regression guard, EMI-5967): the pre-fix mock settles the link but lists nothing</t>
+  </si>
+  <si>
+    <t>Bill Payment Link — Wallet Payment On WebKit (BPL-13, EMI-6039)</t>
+  </si>
+  <si>
+    <t>BPL-13: a wallet payment link submits successfully when location is granted</t>
+  </si>
+  <si>
+    <t>Skipped: EMI-6039 is Safari-specific — run this project against WebKit to reproduce it</t>
+  </si>
+  <si>
+    <t>BPL-13b: the page reads a granted geolocation rather than reporting it blocked</t>
+  </si>
+  <si>
+    <t>BPL-13c: the location-permission error is not shown when permission is granted</t>
+  </si>
+  <si>
     <t>BusinessTestCases/PaymentLinks/functional/GuestWalletPayment.spec.ts</t>
   </si>
   <si>
     <t>Guest Flow — Wallet Payment Link Resolution (GF-01, GF-02)</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>GF-02: a guest with no session should resolve a valid wallet link and see a sanitized summary</t>
   </si>
   <si>
-    <t>Active</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
-    <t>route mocking</t>
-  </si>
-  <si>
     <t>Guest Flow — Bill Payment Link Resolution (GF-03)</t>
   </si>
   <si>
@@ -131,6 +248,9 @@
     <t>TC-PL-014: cancelling from the card payment page should show a result state, not spin forever</t>
   </si>
   <si>
+    <t>Gated: Cancel button not shown for this link/environment</t>
+  </si>
+  <si>
     <t>Payment Link Bugs — Bill Link Does Not Redirect to Wallet (TC-PL-015, EMI-5814)</t>
   </si>
   <si>
@@ -170,9 +290,6 @@
     <t>TC-PL-001 / TC-PL-002: should resolve a valid token and display the payment summary</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>TC-PL-003: should show an error for an invalid or expired token</t>
   </si>
   <si>
@@ -182,6 +299,9 @@
     <t>TC-PL-004: should validate payer info fields and allow payment method selection</t>
   </si>
   <si>
+    <t>Gated: Payer info form retired in favor of server-resolved checkout</t>
+  </si>
+  <si>
     <t>Payment Links — Wallet Link Amount Validation (TC-PL-005, TC-PL-006)</t>
   </si>
   <si>
@@ -197,28 +317,28 @@
     <t>TC-PL-007: should send and display OTP verification after payer info is completed</t>
   </si>
   <si>
-    <t>route mocking; conditionally skipped at runtime if !otpVisible — OTP step not configured for this link/environment</t>
-  </si>
-  <si>
     <t>Payment Links — Full Navigation Flow (TC-PL-008)</t>
   </si>
   <si>
     <t>TC-PL-008: should transition Link Entry → Summary → Payer Info → OTP → Payment → Result with proper state</t>
   </si>
   <si>
+    <t>Gated: Payer info form retired in favor of server-resolved checkout — see PaymentLinkPayerInfoRemoval.spec.ts</t>
+  </si>
+  <si>
     <t>Summary — PaymentLinks</t>
   </si>
   <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-26T17:32:41.318Z</t>
+    <t>2026-09-08T15:08:53.493Z</t>
   </si>
   <si>
     <t>Total test cases</t>
   </si>
   <si>
-    <t>Count per sub-folder (ui / functional / api / archive)</t>
+    <t>Count per sub-folder</t>
   </si>
   <si>
     <t>functional</t>
@@ -233,7 +353,10 @@
     <t>Archived</t>
   </si>
   <si>
-    <t>Spec files in this module</t>
+    <t>Gated behind an env flag</t>
+  </si>
+  <si>
+    <t>Spec files</t>
   </si>
 </sst>
 </file>
@@ -251,6 +374,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b/>
@@ -260,7 +384,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,11 +394,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -292,8 +411,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -635,18 +758,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,36 +801,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -715,54 +841,54 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -779,48 +905,48 @@
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
+    </row>
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -831,54 +957,54 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
+    </row>
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -904,39 +1030,39 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -947,170 +1073,170 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="G14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1118,57 +1244,57 @@
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1176,16 +1302,16 @@
         <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>14</v>
@@ -1194,39 +1320,39 @@
         <v>15</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" t="s">
-        <v>52</v>
-      </c>
-      <c r="I20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1234,57 +1360,57 @@
         <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1292,57 +1418,57 @@
         <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24">
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D24" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1350,58 +1476,725 @@
         <v>9</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="G27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="2" t="s">
+      <c r="G28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="E29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" t="s">
-        <v>16</v>
+      <c r="E30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I49"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1409,65 +2202,96 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>104</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="4"/>
+        <v>110</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1475,18 +2299,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="4">
-        <v>4</v>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
